--- a/config/sdt_templates/CRS620MI_API.xlsx
+++ b/config/sdt_templates/CRS620MI_API.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\w10itasv\Documents\DevDataMigration\DevDataMigrationTool\GitHubDataMigration\DataMigrationTool\config\sdt_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D3D4B0-5ED6-4F54-A0A4-7CE220DB33B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1885D1C3-B05F-4F8B-BF7A-8B00ECD1EF34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="936" xr2:uid="{120A7666-F877-4E64-A298-ACE8E2898CE8}"/>
   </bookViews>
@@ -3882,6 +3882,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Benjamin Nowak</author>
+    <author>Warren Massey</author>
   </authors>
   <commentList>
     <comment ref="B2" authorId="0" shapeId="0" xr:uid="{3BCCCDF4-BDC5-4ACC-8C79-38BFFB9E6491}">
@@ -4359,6 +4360,25 @@
         </r>
       </text>
     </comment>
+    <comment ref="AA2" authorId="1" shapeId="0" xr:uid="{759DDE09-6A97-455C-A547-6E2C842ED74D}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Field type  : A_x000D_
+Field length: 10_x000D_
+Input/Output: OUT_x000D_
+Position    : 16_x000D_
+Mandatory   : False_x000D_
+(Created: 2024-11-20 4:09:18 PM)</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B3" authorId="0" shapeId="0" xr:uid="{97AB17A1-65D2-479E-9B23-EECEC2DA69C4}">
       <text>
         <r>
@@ -4776,6 +4796,23 @@
             <color indexed="81"/>
             <rFont val="Courier New"/>
             <family val="3"/>
+          </rPr>
+          <t>Control Codes: _x000D_
+T : Truncate to field length_x000D_
+U : Convert to Uppercase_x000D_
+B : Send blank values</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AA3" authorId="1" shapeId="0" xr:uid="{A2A9B283-5701-4E2B-BA52-1D8ABCCE4ADE}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>Control Codes: _x000D_
 T : Truncate to field length_x000D_
@@ -4792,6 +4829,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Benjamin Nowak</author>
+    <author>Warren Massey</author>
   </authors>
   <commentList>
     <comment ref="B2" authorId="0" shapeId="0" xr:uid="{91DF2902-2B02-4548-98ED-DBAF497BDD35}">
@@ -4965,6 +5003,25 @@
         </r>
       </text>
     </comment>
+    <comment ref="K2" authorId="1" shapeId="0" xr:uid="{13007AE7-609D-49BF-BE40-FF5450595C57}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Field type  : A_x000D_
+Field length: 10_x000D_
+Input/Output: OUT_x000D_
+Position    : 16_x000D_
+Mandatory   : False_x000D_
+(Created: 2024-11-20 4:09:18 PM)</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B3" authorId="0" shapeId="0" xr:uid="{E5084A2B-9BFE-4BBE-914F-52DB524AA3D6}">
       <text>
         <r>
@@ -5110,6 +5167,23 @@
             <color indexed="81"/>
             <rFont val="Courier New"/>
             <family val="3"/>
+          </rPr>
+          <t>Control Codes: _x000D_
+T : Truncate to field length_x000D_
+U : Convert to Uppercase_x000D_
+B : Send blank values</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="1" shapeId="0" xr:uid="{8416497C-F538-4867-85AC-39ADB8FE67A8}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>Control Codes: _x000D_
 T : Truncate to field length_x000D_
@@ -5185,6 +5259,25 @@
         </r>
       </text>
     </comment>
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{F4FC07EB-651B-41FD-A19E-CB09DDB48268}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Field type  : A_x000D_
+Field length: 10_x000D_
+Input/Output: OUT_x000D_
+Position    : 16_x000D_
+Mandatory   : False_x000D_
+(Created: 2024-11-20 4:09:18 PM)</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B3" authorId="0" shapeId="0" xr:uid="{25E371C5-B32C-4D26-9A04-291DEE4DB996}">
       <text>
         <r>
@@ -5228,6 +5321,23 @@
             <color indexed="81"/>
             <rFont val="Courier New"/>
             <family val="3"/>
+          </rPr>
+          <t>Control Codes: _x000D_
+T : Truncate to field length_x000D_
+U : Convert to Uppercase_x000D_
+B : Send blank values</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{C697567F-8A95-40BB-9185-F4F7D0B8040E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>Control Codes: _x000D_
 T : Truncate to field length_x000D_
@@ -5265,6 +5375,25 @@
         </r>
       </text>
     </comment>
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{3AB25077-3240-4E27-8698-2F6D3903027A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Field type  : A_x000D_
+Field length: 10_x000D_
+Input/Output: OUT_x000D_
+Position    : 16_x000D_
+Mandatory   : False_x000D_
+(Created: 2024-11-20 4:09:18 PM)</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B3" authorId="0" shapeId="0" xr:uid="{704E06D3-7B92-47A0-BE25-12F161CB11FA}">
       <text>
         <r>
@@ -5274,6 +5403,23 @@
             <color indexed="81"/>
             <rFont val="Courier New"/>
             <family val="3"/>
+          </rPr>
+          <t>Control Codes: _x000D_
+T : Truncate to field length_x000D_
+U : Convert to Uppercase_x000D_
+B : Send blank values</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{50D992F0-B4C4-414D-AE5C-3D343A73EBAB}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>Control Codes: _x000D_
 T : Truncate to field length_x000D_
@@ -5368,6 +5514,25 @@
         </r>
       </text>
     </comment>
+    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{3E1FAAA5-95B4-4E3B-B07B-19542203E997}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Field type  : A_x000D_
+Field length: 10_x000D_
+Input/Output: OUT_x000D_
+Position    : 16_x000D_
+Mandatory   : False_x000D_
+(Created: 2024-11-20 4:09:18 PM)</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B3" authorId="0" shapeId="0" xr:uid="{B803D1AE-CE77-450F-92EB-8460CAC7F39C}">
       <text>
         <r>
@@ -5428,6 +5593,23 @@
             <color indexed="81"/>
             <rFont val="Courier New"/>
             <family val="3"/>
+          </rPr>
+          <t>Control Codes: _x000D_
+T : Truncate to field length_x000D_
+U : Convert to Uppercase_x000D_
+B : Send blank values</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{D90105EF-363E-464E-8166-20C6C031121F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>Control Codes: _x000D_
 T : Truncate to field length_x000D_
@@ -5441,7 +5623,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="261">
   <si>
     <t>MESSAGE</t>
   </si>
@@ -7639,13 +7821,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{959C09DD-24BF-4309-8BDD-96A5434F29E8}">
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="26" width="8.88671875" style="2"/>
+    <col min="27" max="27" width="9.109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7724,8 +7907,11 @@
       <c r="Z1" s="2" t="s">
         <v>90</v>
       </c>
+      <c r="AA1" s="2" t="s">
+        <v>101</v>
+      </c>
     </row>
-    <row r="2" spans="1:26" ht="127.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" ht="127.8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>102</v>
       </c>
@@ -7804,8 +7990,11 @@
       <c r="Z2" s="4" t="s">
         <v>175</v>
       </c>
+      <c r="AA2" s="4" t="s">
+        <v>186</v>
+      </c>
     </row>
-    <row r="3" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>187</v>
       </c>
@@ -7884,11 +8073,14 @@
       <c r="Z3" s="6" t="s">
         <v>188</v>
       </c>
+      <c r="AA3" s="6" t="s">
+        <v>187</v>
+      </c>
     </row>
-    <row r="4" spans="1:26" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:27" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:Z3" xr:uid="{8925E76B-ABC6-4615-A369-002E476D11F2}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:AA3" xr:uid="{8925E76B-ABC6-4615-A369-002E476D11F2}">
       <formula1>"yes,yes|Opt:T,yes|Opt:U,yes|Opt:B,yes|Opt:T/U,yes|Opt:T/B,yes|Opt:U/B,yes|Opt:T/U/B,no"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7899,13 +8091,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5517335F-3853-43B9-9D42-F8DBEF8B0855}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="10" width="8.88671875" style="2"/>
+    <col min="11" max="11" width="9.109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7936,8 +8129,11 @@
       <c r="J1" s="2" t="s">
         <v>249</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>101</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" ht="184.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="184.2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>102</v>
       </c>
@@ -7968,8 +8164,11 @@
       <c r="J2" s="4" t="s">
         <v>254</v>
       </c>
+      <c r="K2" s="4" t="s">
+        <v>186</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>187</v>
       </c>
@@ -8000,11 +8199,14 @@
       <c r="J3" s="6" t="s">
         <v>188</v>
       </c>
+      <c r="K3" s="6" t="s">
+        <v>187</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:11" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:J3" xr:uid="{270233E7-573D-426A-A05D-7C7C9C58F9B9}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:K3" xr:uid="{270233E7-573D-426A-A05D-7C7C9C58F9B9}">
       <formula1>"yes,yes|Opt:T,yes|Opt:U,yes|Opt:B,yes|Opt:T/U,yes|Opt:T/B,yes|Opt:U/B,yes|Opt:T/U/B,no"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8015,13 +8217,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E973AD2A-3DD7-4603-A439-E63ECDCE7E51}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="4" width="9.109375" style="2"/>
+    <col min="5" max="5" width="9.109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8034,8 +8237,11 @@
       <c r="D1" s="1" t="s">
         <v>246</v>
       </c>
+      <c r="E1" s="2" t="s">
+        <v>101</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" ht="75.599999999999994" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="75.599999999999994" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>102</v>
       </c>
@@ -8048,8 +8254,11 @@
       <c r="D2" s="4" t="s">
         <v>251</v>
       </c>
+      <c r="E2" s="4" t="s">
+        <v>186</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>187</v>
       </c>
@@ -8062,11 +8271,14 @@
       <c r="D3" s="6" t="s">
         <v>188</v>
       </c>
+      <c r="E3" s="6" t="s">
+        <v>187</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:D3" xr:uid="{C376406B-BCCD-4361-ACAD-EAA4C131A238}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:E3" xr:uid="{C376406B-BCCD-4361-ACAD-EAA4C131A238}">
       <formula1>"yes,yes|Opt:T,yes|Opt:U,yes|Opt:B,yes|Opt:T/U,yes|Opt:T/B,yes|Opt:U/B,yes|Opt:T/U/B,no"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8077,40 +8289,50 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07DDEB50-9798-4F9D-8D14-DE8276EAD0C9}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.109375" style="2"/>
+    <col min="3" max="3" width="9.109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="2" t="s">
+        <v>101</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>102</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>186</v>
       </c>
+      <c r="C2" s="4" t="s">
+        <v>186</v>
+      </c>
     </row>
-    <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>187</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>188</v>
       </c>
+      <c r="C3" s="6" t="s">
+        <v>187</v>
+      </c>
     </row>
-    <row r="4" spans="1:2" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:B3" xr:uid="{3DB29538-53DD-4FC7-8E9C-DC9FD2060A8A}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:C3" xr:uid="{3DB29538-53DD-4FC7-8E9C-DC9FD2060A8A}">
       <formula1>"yes,yes|Opt:T,yes|Opt:U,yes|Opt:B,yes|Opt:T/U,yes|Opt:T/B,yes|Opt:U/B,yes|Opt:T/U/B,no"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8121,13 +8343,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6D2A5D2-F426-4188-B453-609EC6664E71}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="5" width="9.109375" style="2"/>
+    <col min="6" max="6" width="9.109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8143,8 +8366,11 @@
       <c r="E1" s="2" t="s">
         <v>209</v>
       </c>
+      <c r="F1" s="2" t="s">
+        <v>101</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" ht="75.599999999999994" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="75.599999999999994" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>102</v>
       </c>
@@ -8160,8 +8386,11 @@
       <c r="E2" s="4" t="s">
         <v>227</v>
       </c>
+      <c r="F2" s="4" t="s">
+        <v>186</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>187</v>
       </c>
@@ -8177,11 +8406,14 @@
       <c r="E3" s="6" t="s">
         <v>188</v>
       </c>
+      <c r="F3" s="6" t="s">
+        <v>187</v>
+      </c>
     </row>
-    <row r="4" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:E3" xr:uid="{03B93B0E-A14B-4ABB-8E07-C153C650CDC4}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:F3" xr:uid="{03B93B0E-A14B-4ABB-8E07-C153C650CDC4}">
       <formula1>"yes,yes|Opt:T,yes|Opt:U,yes|Opt:B,yes|Opt:T/U,yes|Opt:T/B,yes|Opt:U/B,yes|Opt:T/U/B,no"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8200,15 +8432,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D07E49440B80604690F1C85658D62901" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="87590b8c244ed15461d4796f3ea00467">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4469f008-0876-446a-8a11-ab57c433c4e9" xmlns:ns3="a9379e42-b7ab-4d3d-b629-3fc0de06bd89" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5eb8b56dcf1438251f5c47ae7a44c33b" ns2:_="" ns3:_="">
     <xsd:import namespace="4469f008-0876-446a-8a11-ab57c433c4e9"/>
@@ -8449,6 +8672,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -8467,14 +8699,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CC101B8-7BF2-4938-A9F0-7D2473120737}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9F5B1D4-3BF2-4E51-9D9E-59D25686D47A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8493,6 +8717,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CC101B8-7BF2-4938-A9F0-7D2473120737}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{073E69D9-4508-490E-9F2B-5D3280632237}">
   <ds:schemaRefs>
